--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.55.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.55.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.55.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.55.xlsx
@@ -423,21 +423,21 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="39" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -599,14 +599,22 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: nto evidence ； but the Plaintiff might and still</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: (as the â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]The</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]The</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L24: isolated marker/symbol line :: .</t>
@@ -624,7 +632,11 @@
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The P</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -645,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -657,7 +669,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ The P</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: (as the €</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -702,7 +714,11 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The P</t>
+        </is>
+      </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
@@ -726,12 +742,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -921,12 +937,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -965,7 +981,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1082,7 +1098,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
